--- a/data/Edison's Scores.xlsx
+++ b/data/Edison's Scores.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="633">
   <si>
     <t>Course</t>
   </si>
@@ -171,6 +171,15 @@
     <t>Viera East</t>
   </si>
   <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>PGA National - Front</t>
+  </si>
+  <si>
+    <t>PGA National - Back</t>
+  </si>
+  <si>
     <t>Turtle Creek</t>
   </si>
   <si>
@@ -1780,6 +1789,132 @@
   </si>
   <si>
     <t>4,232,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>5,426,3,3,6,Y</t>
+  </si>
+  <si>
+    <t>4,330,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,257,3,3,6,Y</t>
+  </si>
+  <si>
+    <t>3,120,1,2,3,Y</t>
+  </si>
+  <si>
+    <t>4,316,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,292,2,3,5,Y</t>
+  </si>
+  <si>
+    <t>3,125,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,320,3,3,6,X</t>
+  </si>
+  <si>
+    <t>5,399,4,3,7,X</t>
+  </si>
+  <si>
+    <t>5,404,2,3,5,Y</t>
+  </si>
+  <si>
+    <t>4,312,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,321,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>3,108,2,2,4,X</t>
+  </si>
+  <si>
+    <t>5,355,5,2,7,Y</t>
+  </si>
+  <si>
+    <t>4,281,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>3,107,3,0,3,X</t>
+  </si>
+  <si>
+    <t>4,277,3,3,6,Y</t>
+  </si>
+  <si>
+    <t>4,288,2,2,4,X</t>
+  </si>
+  <si>
+    <t>5,370,7,3,10,Y</t>
+  </si>
+  <si>
+    <t>4,275,3,2,5,X</t>
+  </si>
+  <si>
+    <t>4,280,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>5,365,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>3,105,3,2,5,X</t>
+  </si>
+  <si>
+    <t>4,280,3,3,6,X</t>
+  </si>
+  <si>
+    <t>4,280,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,260,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,275,3,1,4,X</t>
+  </si>
+  <si>
+    <t>4,250,3,4,7,X</t>
+  </si>
+  <si>
+    <t>5,380,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>4,270,2,1,3,Y</t>
+  </si>
+  <si>
+    <t>3,95,4,1,5,X</t>
+  </si>
+  <si>
+    <t>5,365,4,1,5,Y</t>
+  </si>
+  <si>
+    <t>5,370,4,2,6,Y</t>
+  </si>
+  <si>
+    <t>4,275,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,280,2,1,3,Y</t>
+  </si>
+  <si>
+    <t>3,105,2,1,3,X</t>
+  </si>
+  <si>
+    <t>4,280,4,1,5,Y</t>
+  </si>
+  <si>
+    <t>4,275,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>4,250,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>5,380,5,2,7,X</t>
+  </si>
+  <si>
+    <t>4,270,4,2,6,Y</t>
+  </si>
+  <si>
+    <t>5,365,4,3,7,Y</t>
   </si>
 </sst>
 </file>
@@ -1787,7 +1922,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1804,12 +1939,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1841,7 +1970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1873,17 +2002,14 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1896,9 +2022,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2206,7 +2329,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="18.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="15" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="7" width="12.576428571428572" customWidth="1" bestFit="1"/>
@@ -2217,7 +2340,7 @@
     <col min="10" max="10" style="7" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="7" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="7" width="12.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="19" width="12.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="12.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -2263,42 +2386,42 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3">
         <v>44661</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" s="16">
+        <v>64</v>
+      </c>
+      <c r="M2" s="15">
         <v>57</v>
       </c>
     </row>
@@ -2307,39 +2430,39 @@
         <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3">
         <v>44677</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3" s="16">
+        <v>73</v>
+      </c>
+      <c r="M3" s="15">
         <v>51</v>
       </c>
     </row>
@@ -2348,39 +2471,39 @@
         <v>46</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3">
         <v>44682</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="16">
+        <v>81</v>
+      </c>
+      <c r="M4" s="15">
         <v>50</v>
       </c>
     </row>
@@ -2389,39 +2512,39 @@
         <v>49</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3">
         <v>44696</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M5" s="16">
+        <v>88</v>
+      </c>
+      <c r="M5" s="15">
         <v>52</v>
       </c>
     </row>
@@ -2430,39 +2553,39 @@
         <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3">
         <v>44709</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M6" s="16">
+        <v>93</v>
+      </c>
+      <c r="M6" s="15">
         <v>53</v>
       </c>
     </row>
@@ -2471,39 +2594,39 @@
         <v>43</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3">
         <v>44737</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="16">
+        <v>99</v>
+      </c>
+      <c r="M7" s="15">
         <v>52</v>
       </c>
     </row>
@@ -2512,39 +2635,39 @@
         <v>45</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3">
         <v>44849</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M8" s="16">
+        <v>107</v>
+      </c>
+      <c r="M8" s="15">
         <v>45</v>
       </c>
     </row>
@@ -2553,39 +2676,39 @@
         <v>46</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3">
         <v>44863</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M9" s="16">
+        <v>115</v>
+      </c>
+      <c r="M9" s="15">
         <v>54</v>
       </c>
     </row>
@@ -2594,39 +2717,39 @@
         <v>43</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3">
         <v>44870</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>114</v>
+        <v>116</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" s="16">
+        <v>99</v>
+      </c>
+      <c r="M10" s="15">
         <v>46</v>
       </c>
     </row>
@@ -2635,80 +2758,80 @@
         <v>46</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3">
         <v>44878</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="M11" s="16">
+        <v>126</v>
+      </c>
+      <c r="M11" s="15">
         <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3">
         <v>44884</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M12" s="16">
+        <v>128</v>
+      </c>
+      <c r="M12" s="15">
         <v>45</v>
       </c>
     </row>
@@ -2717,39 +2840,39 @@
         <v>43</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C13" s="3">
         <v>44898</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="M13" s="16">
+        <v>135</v>
+      </c>
+      <c r="M13" s="15">
         <v>45</v>
       </c>
     </row>
@@ -2758,80 +2881,80 @@
         <v>46</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C14" s="3">
         <v>45017</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="M14" s="16">
+        <v>144</v>
+      </c>
+      <c r="M14" s="15">
         <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3">
         <v>45031</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M15" s="16">
+        <v>153</v>
+      </c>
+      <c r="M15" s="15">
         <v>49</v>
       </c>
     </row>
@@ -2840,39 +2963,39 @@
         <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3">
         <v>45052</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="M16" s="16">
+        <v>161</v>
+      </c>
+      <c r="M16" s="15">
         <v>38</v>
       </c>
     </row>
@@ -2881,39 +3004,39 @@
         <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C17" s="3">
         <v>45053</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="M17" s="16">
+        <v>168</v>
+      </c>
+      <c r="M17" s="15">
         <v>54</v>
       </c>
     </row>
@@ -2922,80 +3045,80 @@
         <v>43</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C18" s="3">
         <v>45073</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="M18" s="16">
+        <v>175</v>
+      </c>
+      <c r="M18" s="15">
         <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3">
         <v>45081</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="M19" s="16">
+        <v>181</v>
+      </c>
+      <c r="M19" s="15">
         <v>46</v>
       </c>
     </row>
@@ -3004,119 +3127,119 @@
         <v>45</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3">
         <v>45087</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="M20" s="16">
+        <v>191</v>
+      </c>
+      <c r="M20" s="15">
         <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3">
         <v>45088</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M21" s="16">
+        <v>182</v>
+      </c>
+      <c r="M21" s="15">
         <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25">
       <c r="A22" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C22" s="3">
         <v>45116</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="G22" s="18" t="s">
+      <c r="D22" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="F22" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="J22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="K22" s="18" t="s">
+      <c r="H22" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="L22" s="18" t="s">
-        <v>201</v>
+      <c r="I22" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="M22" s="12">
         <v>45</v>
@@ -3124,40 +3247,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
       <c r="A23" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C23" s="3">
         <v>45129</v>
       </c>
-      <c r="D23" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="H23" s="18" t="s">
+      <c r="D23" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="E23" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="F23" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="J23" s="18" t="s">
+      <c r="G23" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="K23" s="18" t="s">
+      <c r="H23" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="L23" s="18" t="s">
+      <c r="I23" s="17" t="s">
         <v>213</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>216</v>
       </c>
       <c r="M23" s="12">
         <v>45</v>
@@ -3165,40 +3288,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25">
       <c r="A24" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C24" s="3">
         <v>45165</v>
       </c>
-      <c r="D24" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="H24" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="L24" s="17" t="s">
         <v>216</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>213</v>
       </c>
       <c r="M24" s="12">
         <v>45</v>
@@ -3206,40 +3329,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
       <c r="A25" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C25" s="3">
         <v>45171</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="G25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="E25" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="F25" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="G25" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="K25" s="18" t="s">
+      <c r="H25" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="L25" s="18" t="s">
+      <c r="I25" s="17" t="s">
         <v>230</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>233</v>
       </c>
       <c r="M25" s="12">
         <v>47</v>
@@ -3247,40 +3370,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
       <c r="A26" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C26" s="3">
         <v>45172</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="H26" s="18" t="s">
+      <c r="D26" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="I26" s="18" t="s">
+      <c r="E26" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="F26" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="J26" s="18" t="s">
+      <c r="G26" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="H26" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="L26" s="18" t="s">
+      <c r="I26" s="17" t="s">
         <v>238</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>241</v>
       </c>
       <c r="M26" s="12">
         <v>45</v>
@@ -3288,40 +3411,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
       <c r="A27" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C27" s="3">
         <v>45179</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M27" s="12">
         <v>49</v>
@@ -3329,40 +3452,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.25">
       <c r="A28" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C28" s="3">
         <v>45186</v>
       </c>
-      <c r="D28" s="18" t="s">
-        <v>248</v>
+      <c r="D28" s="17" t="s">
+        <v>251</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="H28" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="F28" s="17" t="s">
         <v>253</v>
       </c>
+      <c r="G28" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>256</v>
+      </c>
       <c r="J28" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>255</v>
+        <v>257</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>258</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M28" s="12">
         <v>41</v>
@@ -3370,40 +3493,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
       <c r="A29" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C29" s="3">
         <v>45206</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M29" s="12">
         <v>42</v>
@@ -3411,40 +3534,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25">
       <c r="A30" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C30" s="3">
         <v>45207</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="K30" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M30" s="12">
         <v>42</v>
@@ -3452,40 +3575,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20.25">
       <c r="A31" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C31" s="3">
         <v>45208</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M31" s="12">
         <v>49</v>
@@ -3493,40 +3616,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="20.25">
       <c r="A32" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C32" s="3">
         <v>45220</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M32" s="12">
         <v>39</v>
@@ -3537,37 +3660,37 @@
         <v>49</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C33" s="3">
         <v>45221</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M33" s="12">
         <v>42</v>
@@ -3575,40 +3698,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20.25">
       <c r="A34" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C34" s="5">
         <v>45228</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M34" s="12">
         <v>45</v>
@@ -3619,37 +3742,37 @@
         <v>43</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C35" s="3">
         <v>45253</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M35" s="12">
         <v>43</v>
@@ -3657,40 +3780,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
       <c r="A36" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C36" s="5">
         <v>45249</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M36" s="12">
         <v>41</v>
@@ -3701,37 +3824,37 @@
         <v>46</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C37" s="3">
         <v>45298</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M37" s="12">
         <v>42</v>
@@ -3739,40 +3862,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="20.25">
       <c r="A38" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C38" s="3">
         <v>45306</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M38" s="12">
         <v>39</v>
@@ -3780,40 +3903,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="20.25">
       <c r="A39" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C39" s="3">
         <v>45307</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M39" s="12">
         <v>40</v>
@@ -3821,40 +3944,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="20.25">
       <c r="A40" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C40" s="3">
         <v>45389</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M40" s="12">
         <v>46</v>
@@ -3865,37 +3988,37 @@
         <v>45</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C41" s="3">
         <v>45396</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M41" s="12">
         <v>44</v>
@@ -3906,37 +4029,37 @@
         <v>49</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C42" s="3">
         <v>45409</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M42" s="12">
         <v>44</v>
@@ -3947,37 +4070,37 @@
         <v>46</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C43" s="3">
         <v>45410</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M43" s="12">
         <v>50</v>
@@ -3985,40 +4108,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
       <c r="A44" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C44" s="3">
         <v>45445</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="I44" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M44" s="12">
         <v>44</v>
@@ -4026,40 +4149,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="20.25">
       <c r="A45" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C45" s="3">
         <v>45451</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="H45" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M45" s="12">
         <v>44</v>
@@ -4067,40 +4190,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="20.25">
       <c r="A46" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C46" s="3">
         <v>45452</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="H46" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M46" s="12">
         <v>48</v>
@@ -4108,40 +4231,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="20.25">
       <c r="A47" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C47" s="3">
         <v>45466</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M47" s="12">
         <v>50</v>
@@ -4149,40 +4272,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="20.25">
       <c r="A48" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C48" s="3">
         <v>45472</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M48" s="12">
         <v>38</v>
@@ -4190,40 +4313,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="20.25">
       <c r="A49" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C49" s="3">
         <v>45478</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M49" s="12">
         <v>40</v>
@@ -4231,40 +4354,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="20.25">
       <c r="A50" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C50" s="3">
         <v>45479</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J50" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="K50" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M50" s="12">
         <v>43</v>
@@ -4272,40 +4395,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="20.25">
       <c r="A51" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C51" s="3">
         <v>45494</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M51" s="12">
         <v>43</v>
@@ -4316,37 +4439,37 @@
         <v>45</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C52" s="3">
         <v>45584</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M52" s="12">
         <v>44</v>
@@ -4357,37 +4480,37 @@
         <v>46</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C53" s="3">
         <v>45599</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M53" s="12">
         <v>45</v>
@@ -4395,40 +4518,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C54" s="3">
         <v>45606</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M54" s="12">
         <v>42</v>
@@ -4439,37 +4562,37 @@
         <v>43</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C55" s="3">
         <v>45619</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M55" s="12">
         <v>46</v>
@@ -4480,37 +4603,37 @@
         <v>49</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C56" s="3">
         <v>45620</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M56" s="12">
         <v>45</v>
@@ -4527,31 +4650,31 @@
         <v>45753</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M57" s="12">
         <v>44</v>
@@ -4568,31 +4691,31 @@
         <v>45781</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M58" s="12">
         <v>41</v>
@@ -4609,31 +4732,31 @@
         <v>45795</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M59" s="12">
         <v>44</v>
@@ -4650,31 +4773,31 @@
         <v>45815</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="M60" s="12">
         <v>44</v>
@@ -4691,31 +4814,31 @@
         <v>45816</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M61" s="12">
         <v>47</v>
@@ -4732,31 +4855,31 @@
         <v>45934</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="M62" s="12">
         <v>43</v>
@@ -4773,31 +4896,31 @@
         <v>45935</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M63" s="12">
         <v>38</v>
@@ -4805,7 +4928,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>44</v>
@@ -4814,31 +4937,31 @@
         <v>45941</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M64" s="12">
         <v>42</v>
@@ -4846,7 +4969,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>44</v>
@@ -4855,31 +4978,31 @@
         <v>45941</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M65" s="12">
         <v>41</v>
@@ -4887,7 +5010,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>44</v>
@@ -4896,31 +5019,31 @@
         <v>45942</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M66" s="12">
         <v>44</v>
@@ -4928,7 +5051,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>44</v>
@@ -4937,31 +5060,31 @@
         <v>45942</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M67" s="12">
         <v>46</v>
@@ -4978,31 +5101,31 @@
         <v>45956</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M68" s="12">
         <v>41</v>
@@ -5019,31 +5142,31 @@
         <v>45984</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M69" s="12">
         <v>44</v>
@@ -5060,31 +5183,31 @@
         <v>45991</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="M70" s="12">
         <v>36</v>
@@ -5101,125 +5224,281 @@
         <v>45998</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M71" s="12">
         <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
-      <c r="A72" s="2"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="12"/>
+      <c r="A72" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C72" s="3">
+        <v>46131</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="M72" s="12">
+        <v>46</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
-      <c r="A73" s="2"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="12"/>
+      <c r="A73" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" s="3">
+        <v>46133</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="M73" s="12">
+        <v>42</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
-      <c r="A74" s="2"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="12"/>
+      <c r="A74" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="3">
+        <v>46158</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="M74" s="12">
+        <v>46</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
-      <c r="A75" s="2"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="12"/>
+      <c r="A75" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" s="3">
+        <v>46158</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="M75" s="12">
+        <v>40</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
-      <c r="A76" s="2"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="12"/>
+      <c r="A76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C76" s="3">
+        <v>46159</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="M76" s="12">
+        <v>38</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
-      <c r="A77" s="2"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="12"/>
+      <c r="A77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C77" s="3">
+        <v>46159</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M77" s="12">
+        <v>44</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
       <c r="A78" s="2"/>
@@ -19037,16 +19316,16 @@
     <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="15" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="14" max="14" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
@@ -19561,16 +19840,36 @@
       <c r="T12" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
+      <c r="A13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46131</v>
+      </c>
+      <c r="D13" s="12">
+        <v>24</v>
+      </c>
+      <c r="E13" s="12">
+        <v>2</v>
+      </c>
+      <c r="F13" s="12">
+        <v>2</v>
+      </c>
+      <c r="G13" s="12">
+        <v>1</v>
+      </c>
+      <c r="H13" s="12">
+        <v>5</v>
+      </c>
+      <c r="I13" s="12">
+        <v>3</v>
+      </c>
+      <c r="J13" s="12">
+        <v>46</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="12"/>
@@ -19583,16 +19882,36 @@
       <c r="T13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
+      <c r="A14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46133</v>
+      </c>
+      <c r="D14" s="12">
+        <v>30</v>
+      </c>
+      <c r="E14" s="12">
+        <v>4</v>
+      </c>
+      <c r="F14" s="12">
+        <v>2</v>
+      </c>
+      <c r="G14" s="12">
+        <v>1</v>
+      </c>
+      <c r="H14" s="12">
+        <v>3</v>
+      </c>
+      <c r="I14" s="12">
+        <v>2</v>
+      </c>
+      <c r="J14" s="12">
+        <v>42</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="12"/>
@@ -19605,16 +19924,36 @@
       <c r="T14" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
+      <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46158</v>
+      </c>
+      <c r="D15" s="12">
+        <v>38</v>
+      </c>
+      <c r="E15" s="12">
+        <v>3</v>
+      </c>
+      <c r="F15" s="12">
+        <v>1</v>
+      </c>
+      <c r="G15" s="12">
+        <v>1</v>
+      </c>
+      <c r="H15" s="12">
+        <v>1</v>
+      </c>
+      <c r="I15" s="12">
+        <v>6</v>
+      </c>
+      <c r="J15" s="12">
+        <v>46</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="12"/>
@@ -19627,16 +19966,36 @@
       <c r="T15" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46158</v>
+      </c>
+      <c r="D16" s="12">
+        <v>87</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
+        <v>1</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>4</v>
+      </c>
+      <c r="I16" s="12">
+        <v>4</v>
+      </c>
+      <c r="J16" s="12">
+        <v>40</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="12"/>
@@ -19649,16 +20008,36 @@
       <c r="T16" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46159</v>
+      </c>
+      <c r="D17" s="12">
+        <v>42</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>1</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12">
+        <v>38</v>
+      </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="12"/>
@@ -19671,16 +20050,36 @@
       <c r="T17" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="3">
+        <v>46159</v>
+      </c>
+      <c r="D18" s="12">
+        <v>29</v>
+      </c>
+      <c r="E18" s="12">
+        <v>4</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>2</v>
+      </c>
+      <c r="H18" s="12">
+        <v>1</v>
+      </c>
+      <c r="I18" s="12">
+        <v>3</v>
+      </c>
+      <c r="J18" s="12">
+        <v>44</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="12"/>
@@ -19696,13 +20095,13 @@
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="12"/>
@@ -19718,13 +20117,13 @@
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="12"/>
@@ -19740,13 +20139,13 @@
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="12"/>
@@ -19762,13 +20161,13 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="12"/>
@@ -19784,13 +20183,13 @@
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="12"/>
@@ -19806,13 +20205,13 @@
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="12"/>
@@ -19828,13 +20227,13 @@
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="12"/>
@@ -19850,13 +20249,13 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="12"/>
@@ -19872,13 +20271,13 @@
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="12"/>
@@ -19894,13 +20293,13 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="12"/>
@@ -19916,13 +20315,13 @@
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="12"/>
@@ -19938,13 +20337,13 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="12"/>
@@ -19960,13 +20359,13 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="12"/>
@@ -19982,13 +20381,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="12"/>
@@ -20004,13 +20403,13 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="12"/>
@@ -20026,13 +20425,13 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="12"/>
@@ -20048,13 +20447,13 @@
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="12"/>
@@ -20070,13 +20469,13 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="12"/>
@@ -20092,13 +20491,13 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="12"/>
@@ -20114,13 +20513,13 @@
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="12"/>
@@ -20136,13 +20535,13 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="12"/>
@@ -20158,13 +20557,13 @@
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="12"/>
@@ -20180,13 +20579,13 @@
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="12"/>
@@ -20202,13 +20601,13 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="12"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="12"/>
@@ -20224,13 +20623,13 @@
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
       <c r="M43" s="12"/>
@@ -20246,13 +20645,13 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="12"/>
@@ -20268,13 +20667,13 @@
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
       <c r="M45" s="12"/>
@@ -20290,13 +20689,13 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="12"/>
@@ -20312,13 +20711,13 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
       <c r="M47" s="12"/>
@@ -20334,13 +20733,13 @@
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="12"/>
@@ -20356,13 +20755,13 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
       <c r="M49" s="12"/>
@@ -20378,13 +20777,13 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="12"/>
@@ -20400,13 +20799,13 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
       <c r="M51" s="12"/>
@@ -20422,13 +20821,13 @@
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="12"/>
@@ -20444,13 +20843,13 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
       <c r="M53" s="12"/>
@@ -20466,13 +20865,13 @@
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="12"/>
@@ -20488,13 +20887,13 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
       <c r="M55" s="12"/>
@@ -20510,13 +20909,13 @@
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="12"/>
@@ -20532,13 +20931,13 @@
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="12"/>
@@ -20554,13 +20953,13 @@
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="12"/>
@@ -20576,13 +20975,13 @@
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
       <c r="M59" s="12"/>
@@ -20598,13 +20997,13 @@
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="12"/>
@@ -20620,13 +21019,13 @@
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
       <c r="M61" s="12"/>
@@ -20642,13 +21041,13 @@
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="12"/>
@@ -20664,13 +21063,13 @@
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
       <c r="M63" s="12"/>
@@ -20686,13 +21085,13 @@
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="5"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
       <c r="M64" s="12"/>
@@ -20708,13 +21107,13 @@
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="12"/>
@@ -20730,13 +21129,13 @@
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="5"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
       <c r="M66" s="12"/>
@@ -20752,13 +21151,13 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
       <c r="M67" s="12"/>
@@ -20774,13 +21173,13 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
       <c r="M68" s="12"/>
@@ -20796,13 +21195,13 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
       <c r="M69" s="12"/>
@@ -20818,13 +21217,13 @@
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="12"/>
@@ -20840,13 +21239,13 @@
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
       <c r="M71" s="12"/>
@@ -20862,13 +21261,13 @@
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="5"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="12"/>
@@ -20884,13 +21283,13 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="5"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
       <c r="M73" s="12"/>
@@ -20906,13 +21305,13 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="5"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="12"/>
@@ -20928,13 +21327,13 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
       <c r="M75" s="12"/>
@@ -20950,13 +21349,13 @@
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="12"/>
@@ -20972,13 +21371,13 @@
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="5"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
       <c r="M77" s="12"/>
@@ -20994,13 +21393,13 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="5"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="12"/>
@@ -21016,13 +21415,13 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="5"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
       <c r="M79" s="12"/>
@@ -21038,13 +21437,13 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="5"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="12"/>
@@ -21060,13 +21459,13 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="5"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
       <c r="M81" s="12"/>
@@ -21082,13 +21481,13 @@
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="5"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
       <c r="M82" s="12"/>
@@ -21104,13 +21503,13 @@
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="5"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
       <c r="M83" s="12"/>
@@ -21126,13 +21525,13 @@
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="5"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
       <c r="M84" s="12"/>
@@ -21148,13 +21547,13 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="5"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="13"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
       <c r="M85" s="12"/>
@@ -21170,13 +21569,13 @@
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="5"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="13"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="12"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="12"/>
@@ -21192,13 +21591,13 @@
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="5"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
-      <c r="J87" s="13"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
+      <c r="I87" s="12"/>
+      <c r="J87" s="12"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
       <c r="M87" s="12"/>
@@ -21214,13 +21613,13 @@
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="5"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
-      <c r="J88" s="13"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="12"/>
@@ -21236,13 +21635,13 @@
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="5"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
+      <c r="I89" s="12"/>
+      <c r="J89" s="12"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
       <c r="M89" s="12"/>
@@ -21258,13 +21657,13 @@
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="5"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="12"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="12"/>
@@ -21280,13 +21679,13 @@
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="5"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="13"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="12"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="12"/>
@@ -21302,13 +21701,13 @@
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="5"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
-      <c r="J92" s="13"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
+      <c r="I92" s="12"/>
+      <c r="J92" s="12"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="12"/>
@@ -21324,13 +21723,13 @@
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="5"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="13"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
+      <c r="I93" s="12"/>
+      <c r="J93" s="12"/>
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
       <c r="M93" s="12"/>
@@ -21346,13 +21745,13 @@
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="5"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="13"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="12"/>
@@ -21368,13 +21767,13 @@
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="5"/>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
-      <c r="J95" s="13"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
+      <c r="I95" s="12"/>
+      <c r="J95" s="12"/>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
       <c r="M95" s="12"/>
@@ -21390,13 +21789,13 @@
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="5"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="12"/>
@@ -21412,13 +21811,13 @@
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="5"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="12"/>
@@ -21434,13 +21833,13 @@
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="5"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="12"/>
@@ -21456,13 +21855,13 @@
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="5"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
       <c r="M99" s="12"/>
@@ -21478,13 +21877,13 @@
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="5"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="13"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="12"/>
@@ -21500,13 +21899,13 @@
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="5"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
       <c r="M101" s="12"/>
@@ -21522,13 +21921,13 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="5"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
+      <c r="I102" s="12"/>
+      <c r="J102" s="12"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="12"/>
@@ -21544,13 +21943,13 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="5"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
-      <c r="J103" s="13"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="12"/>
+      <c r="I103" s="12"/>
+      <c r="J103" s="12"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
       <c r="M103" s="12"/>
@@ -21566,13 +21965,13 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="5"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
-      <c r="J104" s="13"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+      <c r="H104" s="12"/>
+      <c r="I104" s="12"/>
+      <c r="J104" s="12"/>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="12"/>
@@ -21588,13 +21987,13 @@
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="5"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="13"/>
-      <c r="J105" s="13"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+      <c r="H105" s="12"/>
+      <c r="I105" s="12"/>
+      <c r="J105" s="12"/>
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
       <c r="M105" s="12"/>
@@ -21610,13 +22009,13 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="5"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
-      <c r="I106" s="13"/>
-      <c r="J106" s="13"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="12"/>
+      <c r="I106" s="12"/>
+      <c r="J106" s="12"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
       <c r="M106" s="12"/>
@@ -21632,13 +22031,13 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="5"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13"/>
-      <c r="I107" s="13"/>
-      <c r="J107" s="13"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="12"/>
+      <c r="I107" s="12"/>
+      <c r="J107" s="12"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
       <c r="M107" s="12"/>
@@ -21654,13 +22053,13 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="5"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
-      <c r="I108" s="13"/>
-      <c r="J108" s="13"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="12"/>
@@ -21676,13 +22075,13 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="5"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
-      <c r="H109" s="13"/>
-      <c r="I109" s="13"/>
-      <c r="J109" s="13"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+      <c r="H109" s="12"/>
+      <c r="I109" s="12"/>
+      <c r="J109" s="12"/>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
       <c r="M109" s="12"/>
@@ -21698,13 +22097,13 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="5"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="13"/>
-      <c r="H110" s="13"/>
-      <c r="I110" s="13"/>
-      <c r="J110" s="13"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="12"/>
+      <c r="I110" s="12"/>
+      <c r="J110" s="12"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
       <c r="M110" s="12"/>
@@ -21720,13 +22119,13 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="5"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="13"/>
-      <c r="H111" s="13"/>
-      <c r="I111" s="13"/>
-      <c r="J111" s="13"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="12"/>
+      <c r="I111" s="12"/>
+      <c r="J111" s="12"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
       <c r="M111" s="12"/>
@@ -21742,13 +22141,13 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="5"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
-      <c r="I112" s="13"/>
-      <c r="J112" s="13"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="12"/>
+      <c r="I112" s="12"/>
+      <c r="J112" s="12"/>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="12"/>
@@ -21764,13 +22163,13 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="5"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
-      <c r="I113" s="13"/>
-      <c r="J113" s="13"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="12"/>
+      <c r="I113" s="12"/>
+      <c r="J113" s="12"/>
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
       <c r="M113" s="12"/>
@@ -21786,13 +22185,13 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="5"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="H114" s="13"/>
-      <c r="I114" s="13"/>
-      <c r="J114" s="13"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="12"/>
+      <c r="I114" s="12"/>
+      <c r="J114" s="12"/>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
       <c r="M114" s="12"/>
@@ -21808,13 +22207,13 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="5"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="13"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="13"/>
-      <c r="H115" s="13"/>
-      <c r="I115" s="13"/>
-      <c r="J115" s="13"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
+      <c r="I115" s="12"/>
+      <c r="J115" s="12"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
       <c r="M115" s="12"/>
@@ -21830,13 +22229,13 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="5"/>
-      <c r="D116" s="13"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="13"/>
-      <c r="H116" s="13"/>
-      <c r="I116" s="13"/>
-      <c r="J116" s="13"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="12"/>
+      <c r="I116" s="12"/>
+      <c r="J116" s="12"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
       <c r="M116" s="12"/>
@@ -21852,13 +22251,13 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="5"/>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
-      <c r="F117" s="13"/>
-      <c r="G117" s="13"/>
-      <c r="H117" s="13"/>
-      <c r="I117" s="13"/>
-      <c r="J117" s="13"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="12"/>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
       <c r="M117" s="12"/>
@@ -21874,13 +22273,13 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="5"/>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="13"/>
-      <c r="H118" s="13"/>
-      <c r="I118" s="13"/>
-      <c r="J118" s="13"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="12"/>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
       <c r="M118" s="12"/>
@@ -21896,13 +22295,13 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="5"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="13"/>
-      <c r="H119" s="13"/>
-      <c r="I119" s="13"/>
-      <c r="J119" s="13"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="12"/>
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
       <c r="M119" s="12"/>
@@ -21918,13 +22317,13 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="5"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
-      <c r="J120" s="13"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="12"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="12"/>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
       <c r="M120" s="12"/>
@@ -21940,13 +22339,13 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="5"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="13"/>
-      <c r="H121" s="13"/>
-      <c r="I121" s="13"/>
-      <c r="J121" s="13"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
       <c r="M121" s="12"/>
@@ -21962,13 +22361,13 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="5"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="13"/>
-      <c r="H122" s="13"/>
-      <c r="I122" s="13"/>
-      <c r="J122" s="13"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
       <c r="M122" s="12"/>
@@ -21984,13 +22383,13 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="5"/>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
-      <c r="F123" s="13"/>
-      <c r="G123" s="13"/>
-      <c r="H123" s="13"/>
-      <c r="I123" s="13"/>
-      <c r="J123" s="13"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
       <c r="M123" s="12"/>
@@ -22006,13 +22405,13 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="5"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="13"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="13"/>
-      <c r="J124" s="13"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
       <c r="M124" s="12"/>
@@ -22028,13 +22427,13 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="5"/>
-      <c r="D125" s="13"/>
-      <c r="E125" s="13"/>
-      <c r="F125" s="13"/>
-      <c r="G125" s="13"/>
-      <c r="H125" s="13"/>
-      <c r="I125" s="13"/>
-      <c r="J125" s="13"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
+      <c r="I125" s="12"/>
+      <c r="J125" s="12"/>
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
       <c r="M125" s="12"/>
@@ -22050,13 +22449,13 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="5"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
-      <c r="F126" s="13"/>
-      <c r="G126" s="13"/>
-      <c r="H126" s="13"/>
-      <c r="I126" s="13"/>
-      <c r="J126" s="13"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
       <c r="M126" s="12"/>
@@ -22072,13 +22471,13 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="5"/>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
-      <c r="F127" s="13"/>
-      <c r="G127" s="13"/>
-      <c r="H127" s="13"/>
-      <c r="I127" s="13"/>
-      <c r="J127" s="13"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="12"/>
+      <c r="I127" s="12"/>
+      <c r="J127" s="12"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
       <c r="M127" s="12"/>
@@ -22094,13 +22493,13 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="5"/>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
-      <c r="F128" s="13"/>
-      <c r="G128" s="13"/>
-      <c r="H128" s="13"/>
-      <c r="I128" s="13"/>
-      <c r="J128" s="13"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="12"/>
+      <c r="I128" s="12"/>
+      <c r="J128" s="12"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
       <c r="M128" s="12"/>
@@ -22116,13 +22515,13 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="5"/>
-      <c r="D129" s="13"/>
-      <c r="E129" s="13"/>
-      <c r="F129" s="13"/>
-      <c r="G129" s="13"/>
-      <c r="H129" s="13"/>
-      <c r="I129" s="13"/>
-      <c r="J129" s="13"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
+      <c r="H129" s="12"/>
+      <c r="I129" s="12"/>
+      <c r="J129" s="12"/>
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
       <c r="M129" s="12"/>
@@ -22138,13 +22537,13 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="5"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
-      <c r="F130" s="13"/>
-      <c r="G130" s="13"/>
-      <c r="H130" s="13"/>
-      <c r="I130" s="13"/>
-      <c r="J130" s="13"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
       <c r="M130" s="12"/>
@@ -22160,13 +22559,13 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="5"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
-      <c r="F131" s="13"/>
-      <c r="G131" s="13"/>
-      <c r="H131" s="13"/>
-      <c r="I131" s="13"/>
-      <c r="J131" s="13"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="12"/>
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
       <c r="M131" s="12"/>
@@ -22182,13 +22581,13 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="5"/>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
-      <c r="F132" s="13"/>
-      <c r="G132" s="13"/>
-      <c r="H132" s="13"/>
-      <c r="I132" s="13"/>
-      <c r="J132" s="13"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
+      <c r="I132" s="12"/>
+      <c r="J132" s="12"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
       <c r="M132" s="12"/>
@@ -22204,13 +22603,13 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="5"/>
-      <c r="D133" s="13"/>
-      <c r="E133" s="13"/>
-      <c r="F133" s="13"/>
-      <c r="G133" s="13"/>
-      <c r="H133" s="13"/>
-      <c r="I133" s="13"/>
-      <c r="J133" s="13"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="12"/>
+      <c r="I133" s="12"/>
+      <c r="J133" s="12"/>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
       <c r="M133" s="12"/>
@@ -22226,13 +22625,13 @@
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="5"/>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13"/>
-      <c r="G134" s="13"/>
-      <c r="H134" s="13"/>
-      <c r="I134" s="13"/>
-      <c r="J134" s="13"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="12"/>
+      <c r="I134" s="12"/>
+      <c r="J134" s="12"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
       <c r="M134" s="12"/>
@@ -22248,13 +22647,13 @@
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="5"/>
-      <c r="D135" s="13"/>
-      <c r="E135" s="13"/>
-      <c r="F135" s="13"/>
-      <c r="G135" s="13"/>
-      <c r="H135" s="13"/>
-      <c r="I135" s="13"/>
-      <c r="J135" s="13"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
+      <c r="H135" s="12"/>
+      <c r="I135" s="12"/>
+      <c r="J135" s="12"/>
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
       <c r="M135" s="12"/>
@@ -22270,13 +22669,13 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="5"/>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
-      <c r="F136" s="13"/>
-      <c r="G136" s="13"/>
-      <c r="H136" s="13"/>
-      <c r="I136" s="13"/>
-      <c r="J136" s="13"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="12"/>
+      <c r="I136" s="12"/>
+      <c r="J136" s="12"/>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
       <c r="M136" s="12"/>
@@ -22292,13 +22691,13 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="5"/>
-      <c r="D137" s="13"/>
-      <c r="E137" s="13"/>
-      <c r="F137" s="13"/>
-      <c r="G137" s="13"/>
-      <c r="H137" s="13"/>
-      <c r="I137" s="13"/>
-      <c r="J137" s="13"/>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="12"/>
+      <c r="I137" s="12"/>
+      <c r="J137" s="12"/>
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
       <c r="M137" s="12"/>
@@ -22314,13 +22713,13 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="5"/>
-      <c r="D138" s="13"/>
-      <c r="E138" s="13"/>
-      <c r="F138" s="13"/>
-      <c r="G138" s="13"/>
-      <c r="H138" s="13"/>
-      <c r="I138" s="13"/>
-      <c r="J138" s="13"/>
+      <c r="D138" s="12"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="12"/>
+      <c r="I138" s="12"/>
+      <c r="J138" s="12"/>
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
       <c r="M138" s="12"/>
@@ -22336,13 +22735,13 @@
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="5"/>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
-      <c r="F139" s="13"/>
-      <c r="G139" s="13"/>
-      <c r="H139" s="13"/>
-      <c r="I139" s="13"/>
-      <c r="J139" s="13"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
+      <c r="H139" s="12"/>
+      <c r="I139" s="12"/>
+      <c r="J139" s="12"/>
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
       <c r="M139" s="12"/>
@@ -22358,13 +22757,13 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="5"/>
-      <c r="D140" s="13"/>
-      <c r="E140" s="13"/>
-      <c r="F140" s="13"/>
-      <c r="G140" s="13"/>
-      <c r="H140" s="13"/>
-      <c r="I140" s="13"/>
-      <c r="J140" s="13"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
+      <c r="H140" s="12"/>
+      <c r="I140" s="12"/>
+      <c r="J140" s="12"/>
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
       <c r="M140" s="12"/>
@@ -22380,13 +22779,13 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="5"/>
-      <c r="D141" s="13"/>
-      <c r="E141" s="13"/>
-      <c r="F141" s="13"/>
-      <c r="G141" s="13"/>
-      <c r="H141" s="13"/>
-      <c r="I141" s="13"/>
-      <c r="J141" s="13"/>
+      <c r="D141" s="12"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="12"/>
+      <c r="I141" s="12"/>
+      <c r="J141" s="12"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
       <c r="M141" s="12"/>
@@ -22402,13 +22801,13 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="5"/>
-      <c r="D142" s="13"/>
-      <c r="E142" s="13"/>
-      <c r="F142" s="13"/>
-      <c r="G142" s="13"/>
-      <c r="H142" s="13"/>
-      <c r="I142" s="13"/>
-      <c r="J142" s="13"/>
+      <c r="D142" s="12"/>
+      <c r="E142" s="12"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
+      <c r="H142" s="12"/>
+      <c r="I142" s="12"/>
+      <c r="J142" s="12"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
       <c r="M142" s="12"/>
@@ -22424,13 +22823,13 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="5"/>
-      <c r="D143" s="13"/>
-      <c r="E143" s="13"/>
-      <c r="F143" s="13"/>
-      <c r="G143" s="13"/>
-      <c r="H143" s="13"/>
-      <c r="I143" s="13"/>
-      <c r="J143" s="13"/>
+      <c r="D143" s="12"/>
+      <c r="E143" s="12"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
+      <c r="H143" s="12"/>
+      <c r="I143" s="12"/>
+      <c r="J143" s="12"/>
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
       <c r="M143" s="12"/>
@@ -22446,13 +22845,13 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="5"/>
-      <c r="D144" s="13"/>
-      <c r="E144" s="13"/>
-      <c r="F144" s="13"/>
-      <c r="G144" s="13"/>
-      <c r="H144" s="13"/>
-      <c r="I144" s="13"/>
-      <c r="J144" s="13"/>
+      <c r="D144" s="12"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
+      <c r="H144" s="12"/>
+      <c r="I144" s="12"/>
+      <c r="J144" s="12"/>
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
       <c r="M144" s="12"/>
@@ -22468,13 +22867,13 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="5"/>
-      <c r="D145" s="13"/>
-      <c r="E145" s="13"/>
-      <c r="F145" s="13"/>
-      <c r="G145" s="13"/>
-      <c r="H145" s="13"/>
-      <c r="I145" s="13"/>
-      <c r="J145" s="13"/>
+      <c r="D145" s="12"/>
+      <c r="E145" s="12"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
+      <c r="H145" s="12"/>
+      <c r="I145" s="12"/>
+      <c r="J145" s="12"/>
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
       <c r="M145" s="12"/>
@@ -22490,13 +22889,13 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="5"/>
-      <c r="D146" s="13"/>
-      <c r="E146" s="13"/>
-      <c r="F146" s="13"/>
-      <c r="G146" s="13"/>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
-      <c r="J146" s="13"/>
+      <c r="D146" s="12"/>
+      <c r="E146" s="12"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="12"/>
+      <c r="H146" s="12"/>
+      <c r="I146" s="12"/>
+      <c r="J146" s="12"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
       <c r="M146" s="12"/>
@@ -22512,13 +22911,13 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="5"/>
-      <c r="D147" s="13"/>
-      <c r="E147" s="13"/>
-      <c r="F147" s="13"/>
-      <c r="G147" s="13"/>
-      <c r="H147" s="13"/>
-      <c r="I147" s="13"/>
-      <c r="J147" s="13"/>
+      <c r="D147" s="12"/>
+      <c r="E147" s="12"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12"/>
+      <c r="H147" s="12"/>
+      <c r="I147" s="12"/>
+      <c r="J147" s="12"/>
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
       <c r="M147" s="12"/>
@@ -22534,13 +22933,13 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="5"/>
-      <c r="D148" s="13"/>
-      <c r="E148" s="13"/>
-      <c r="F148" s="13"/>
-      <c r="G148" s="13"/>
-      <c r="H148" s="13"/>
-      <c r="I148" s="13"/>
-      <c r="J148" s="13"/>
+      <c r="D148" s="12"/>
+      <c r="E148" s="12"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="12"/>
+      <c r="H148" s="12"/>
+      <c r="I148" s="12"/>
+      <c r="J148" s="12"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
       <c r="M148" s="12"/>
@@ -22556,13 +22955,13 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="5"/>
-      <c r="D149" s="13"/>
-      <c r="E149" s="13"/>
-      <c r="F149" s="13"/>
-      <c r="G149" s="13"/>
-      <c r="H149" s="13"/>
-      <c r="I149" s="13"/>
-      <c r="J149" s="13"/>
+      <c r="D149" s="12"/>
+      <c r="E149" s="12"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="12"/>
+      <c r="H149" s="12"/>
+      <c r="I149" s="12"/>
+      <c r="J149" s="12"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
       <c r="M149" s="12"/>
@@ -22578,13 +22977,13 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="5"/>
-      <c r="D150" s="13"/>
-      <c r="E150" s="13"/>
-      <c r="F150" s="13"/>
-      <c r="G150" s="13"/>
-      <c r="H150" s="13"/>
-      <c r="I150" s="13"/>
-      <c r="J150" s="13"/>
+      <c r="D150" s="12"/>
+      <c r="E150" s="12"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="12"/>
+      <c r="H150" s="12"/>
+      <c r="I150" s="12"/>
+      <c r="J150" s="12"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
       <c r="M150" s="12"/>
@@ -22600,13 +22999,13 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="5"/>
-      <c r="D151" s="13"/>
-      <c r="E151" s="13"/>
-      <c r="F151" s="13"/>
-      <c r="G151" s="13"/>
-      <c r="H151" s="13"/>
-      <c r="I151" s="13"/>
-      <c r="J151" s="13"/>
+      <c r="D151" s="12"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
+      <c r="H151" s="12"/>
+      <c r="I151" s="12"/>
+      <c r="J151" s="12"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
       <c r="M151" s="12"/>
@@ -22622,13 +23021,13 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="5"/>
-      <c r="D152" s="13"/>
-      <c r="E152" s="13"/>
-      <c r="F152" s="13"/>
-      <c r="G152" s="13"/>
-      <c r="H152" s="13"/>
-      <c r="I152" s="13"/>
-      <c r="J152" s="13"/>
+      <c r="D152" s="12"/>
+      <c r="E152" s="12"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="12"/>
+      <c r="H152" s="12"/>
+      <c r="I152" s="12"/>
+      <c r="J152" s="12"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
       <c r="M152" s="12"/>
@@ -22644,13 +23043,13 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="5"/>
-      <c r="D153" s="13"/>
-      <c r="E153" s="13"/>
-      <c r="F153" s="13"/>
-      <c r="G153" s="13"/>
-      <c r="H153" s="13"/>
-      <c r="I153" s="13"/>
-      <c r="J153" s="13"/>
+      <c r="D153" s="12"/>
+      <c r="E153" s="12"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
+      <c r="H153" s="12"/>
+      <c r="I153" s="12"/>
+      <c r="J153" s="12"/>
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
       <c r="M153" s="12"/>
@@ -22666,13 +23065,13 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="5"/>
-      <c r="D154" s="13"/>
-      <c r="E154" s="13"/>
-      <c r="F154" s="13"/>
-      <c r="G154" s="13"/>
-      <c r="H154" s="13"/>
-      <c r="I154" s="13"/>
-      <c r="J154" s="13"/>
+      <c r="D154" s="12"/>
+      <c r="E154" s="12"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="12"/>
+      <c r="H154" s="12"/>
+      <c r="I154" s="12"/>
+      <c r="J154" s="12"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
       <c r="M154" s="12"/>
@@ -22688,13 +23087,13 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="5"/>
-      <c r="D155" s="13"/>
-      <c r="E155" s="13"/>
-      <c r="F155" s="13"/>
-      <c r="G155" s="13"/>
-      <c r="H155" s="13"/>
-      <c r="I155" s="13"/>
-      <c r="J155" s="13"/>
+      <c r="D155" s="12"/>
+      <c r="E155" s="12"/>
+      <c r="F155" s="12"/>
+      <c r="G155" s="12"/>
+      <c r="H155" s="12"/>
+      <c r="I155" s="12"/>
+      <c r="J155" s="12"/>
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
       <c r="M155" s="12"/>
@@ -22710,13 +23109,13 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="5"/>
-      <c r="D156" s="13"/>
-      <c r="E156" s="13"/>
-      <c r="F156" s="13"/>
-      <c r="G156" s="13"/>
-      <c r="H156" s="13"/>
-      <c r="I156" s="13"/>
-      <c r="J156" s="13"/>
+      <c r="D156" s="12"/>
+      <c r="E156" s="12"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="12"/>
+      <c r="H156" s="12"/>
+      <c r="I156" s="12"/>
+      <c r="J156" s="12"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
       <c r="M156" s="12"/>
@@ -22732,13 +23131,13 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="5"/>
-      <c r="D157" s="13"/>
-      <c r="E157" s="13"/>
-      <c r="F157" s="13"/>
-      <c r="G157" s="13"/>
-      <c r="H157" s="13"/>
-      <c r="I157" s="13"/>
-      <c r="J157" s="13"/>
+      <c r="D157" s="12"/>
+      <c r="E157" s="12"/>
+      <c r="F157" s="12"/>
+      <c r="G157" s="12"/>
+      <c r="H157" s="12"/>
+      <c r="I157" s="12"/>
+      <c r="J157" s="12"/>
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
       <c r="M157" s="12"/>
@@ -22754,13 +23153,13 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="5"/>
-      <c r="D158" s="13"/>
-      <c r="E158" s="13"/>
-      <c r="F158" s="13"/>
-      <c r="G158" s="13"/>
-      <c r="H158" s="13"/>
-      <c r="I158" s="13"/>
-      <c r="J158" s="13"/>
+      <c r="D158" s="12"/>
+      <c r="E158" s="12"/>
+      <c r="F158" s="12"/>
+      <c r="G158" s="12"/>
+      <c r="H158" s="12"/>
+      <c r="I158" s="12"/>
+      <c r="J158" s="12"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
       <c r="M158" s="12"/>
@@ -22776,13 +23175,13 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="5"/>
-      <c r="D159" s="13"/>
-      <c r="E159" s="13"/>
-      <c r="F159" s="13"/>
-      <c r="G159" s="13"/>
-      <c r="H159" s="13"/>
-      <c r="I159" s="13"/>
-      <c r="J159" s="13"/>
+      <c r="D159" s="12"/>
+      <c r="E159" s="12"/>
+      <c r="F159" s="12"/>
+      <c r="G159" s="12"/>
+      <c r="H159" s="12"/>
+      <c r="I159" s="12"/>
+      <c r="J159" s="12"/>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
       <c r="M159" s="12"/>
@@ -22798,13 +23197,13 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="5"/>
-      <c r="D160" s="13"/>
-      <c r="E160" s="13"/>
-      <c r="F160" s="13"/>
-      <c r="G160" s="13"/>
-      <c r="H160" s="13"/>
-      <c r="I160" s="13"/>
-      <c r="J160" s="13"/>
+      <c r="D160" s="12"/>
+      <c r="E160" s="12"/>
+      <c r="F160" s="12"/>
+      <c r="G160" s="12"/>
+      <c r="H160" s="12"/>
+      <c r="I160" s="12"/>
+      <c r="J160" s="12"/>
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
       <c r="M160" s="12"/>
@@ -22820,13 +23219,13 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="5"/>
-      <c r="D161" s="13"/>
-      <c r="E161" s="13"/>
-      <c r="F161" s="13"/>
-      <c r="G161" s="13"/>
-      <c r="H161" s="13"/>
-      <c r="I161" s="13"/>
-      <c r="J161" s="13"/>
+      <c r="D161" s="12"/>
+      <c r="E161" s="12"/>
+      <c r="F161" s="12"/>
+      <c r="G161" s="12"/>
+      <c r="H161" s="12"/>
+      <c r="I161" s="12"/>
+      <c r="J161" s="12"/>
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
       <c r="M161" s="12"/>
@@ -22842,13 +23241,13 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="5"/>
-      <c r="D162" s="13"/>
-      <c r="E162" s="13"/>
-      <c r="F162" s="13"/>
-      <c r="G162" s="13"/>
-      <c r="H162" s="13"/>
-      <c r="I162" s="13"/>
-      <c r="J162" s="13"/>
+      <c r="D162" s="12"/>
+      <c r="E162" s="12"/>
+      <c r="F162" s="12"/>
+      <c r="G162" s="12"/>
+      <c r="H162" s="12"/>
+      <c r="I162" s="12"/>
+      <c r="J162" s="12"/>
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
       <c r="M162" s="12"/>
@@ -22864,13 +23263,13 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="5"/>
-      <c r="D163" s="13"/>
-      <c r="E163" s="13"/>
-      <c r="F163" s="13"/>
-      <c r="G163" s="13"/>
-      <c r="H163" s="13"/>
-      <c r="I163" s="13"/>
-      <c r="J163" s="13"/>
+      <c r="D163" s="12"/>
+      <c r="E163" s="12"/>
+      <c r="F163" s="12"/>
+      <c r="G163" s="12"/>
+      <c r="H163" s="12"/>
+      <c r="I163" s="12"/>
+      <c r="J163" s="12"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
       <c r="M163" s="12"/>
@@ -22886,13 +23285,13 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="5"/>
-      <c r="D164" s="13"/>
-      <c r="E164" s="13"/>
-      <c r="F164" s="13"/>
-      <c r="G164" s="13"/>
-      <c r="H164" s="13"/>
-      <c r="I164" s="13"/>
-      <c r="J164" s="13"/>
+      <c r="D164" s="12"/>
+      <c r="E164" s="12"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="12"/>
+      <c r="H164" s="12"/>
+      <c r="I164" s="12"/>
+      <c r="J164" s="12"/>
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
       <c r="M164" s="12"/>
@@ -22908,13 +23307,13 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="5"/>
-      <c r="D165" s="13"/>
-      <c r="E165" s="13"/>
-      <c r="F165" s="13"/>
-      <c r="G165" s="13"/>
-      <c r="H165" s="13"/>
-      <c r="I165" s="13"/>
-      <c r="J165" s="13"/>
+      <c r="D165" s="12"/>
+      <c r="E165" s="12"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="12"/>
+      <c r="H165" s="12"/>
+      <c r="I165" s="12"/>
+      <c r="J165" s="12"/>
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
       <c r="M165" s="12"/>
@@ -22930,13 +23329,13 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="5"/>
-      <c r="D166" s="13"/>
-      <c r="E166" s="13"/>
-      <c r="F166" s="13"/>
-      <c r="G166" s="13"/>
-      <c r="H166" s="13"/>
-      <c r="I166" s="13"/>
-      <c r="J166" s="13"/>
+      <c r="D166" s="12"/>
+      <c r="E166" s="12"/>
+      <c r="F166" s="12"/>
+      <c r="G166" s="12"/>
+      <c r="H166" s="12"/>
+      <c r="I166" s="12"/>
+      <c r="J166" s="12"/>
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
       <c r="M166" s="12"/>
@@ -22952,13 +23351,13 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="5"/>
-      <c r="D167" s="13"/>
-      <c r="E167" s="13"/>
-      <c r="F167" s="13"/>
-      <c r="G167" s="13"/>
-      <c r="H167" s="13"/>
-      <c r="I167" s="13"/>
-      <c r="J167" s="13"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="12"/>
+      <c r="F167" s="12"/>
+      <c r="G167" s="12"/>
+      <c r="H167" s="12"/>
+      <c r="I167" s="12"/>
+      <c r="J167" s="12"/>
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
       <c r="M167" s="12"/>
@@ -22974,13 +23373,13 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="5"/>
-      <c r="D168" s="13"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
-      <c r="G168" s="13"/>
-      <c r="H168" s="13"/>
-      <c r="I168" s="13"/>
-      <c r="J168" s="13"/>
+      <c r="D168" s="12"/>
+      <c r="E168" s="12"/>
+      <c r="F168" s="12"/>
+      <c r="G168" s="12"/>
+      <c r="H168" s="12"/>
+      <c r="I168" s="12"/>
+      <c r="J168" s="12"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
       <c r="M168" s="12"/>
@@ -22996,13 +23395,13 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="5"/>
-      <c r="D169" s="13"/>
-      <c r="E169" s="13"/>
-      <c r="F169" s="13"/>
-      <c r="G169" s="13"/>
-      <c r="H169" s="13"/>
-      <c r="I169" s="13"/>
-      <c r="J169" s="13"/>
+      <c r="D169" s="12"/>
+      <c r="E169" s="12"/>
+      <c r="F169" s="12"/>
+      <c r="G169" s="12"/>
+      <c r="H169" s="12"/>
+      <c r="I169" s="12"/>
+      <c r="J169" s="12"/>
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
       <c r="M169" s="12"/>
@@ -23018,13 +23417,13 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="5"/>
-      <c r="D170" s="13"/>
-      <c r="E170" s="13"/>
-      <c r="F170" s="13"/>
-      <c r="G170" s="13"/>
-      <c r="H170" s="13"/>
-      <c r="I170" s="13"/>
-      <c r="J170" s="13"/>
+      <c r="D170" s="12"/>
+      <c r="E170" s="12"/>
+      <c r="F170" s="12"/>
+      <c r="G170" s="12"/>
+      <c r="H170" s="12"/>
+      <c r="I170" s="12"/>
+      <c r="J170" s="12"/>
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
       <c r="M170" s="12"/>
@@ -23040,13 +23439,13 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="5"/>
-      <c r="D171" s="13"/>
-      <c r="E171" s="13"/>
-      <c r="F171" s="13"/>
-      <c r="G171" s="13"/>
-      <c r="H171" s="13"/>
-      <c r="I171" s="13"/>
-      <c r="J171" s="13"/>
+      <c r="D171" s="12"/>
+      <c r="E171" s="12"/>
+      <c r="F171" s="12"/>
+      <c r="G171" s="12"/>
+      <c r="H171" s="12"/>
+      <c r="I171" s="12"/>
+      <c r="J171" s="12"/>
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
       <c r="M171" s="12"/>
@@ -23062,13 +23461,13 @@
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="5"/>
-      <c r="D172" s="13"/>
-      <c r="E172" s="13"/>
-      <c r="F172" s="13"/>
-      <c r="G172" s="13"/>
-      <c r="H172" s="13"/>
-      <c r="I172" s="13"/>
-      <c r="J172" s="13"/>
+      <c r="D172" s="12"/>
+      <c r="E172" s="12"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
+      <c r="H172" s="12"/>
+      <c r="I172" s="12"/>
+      <c r="J172" s="12"/>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
       <c r="M172" s="12"/>
@@ -23084,13 +23483,13 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="5"/>
-      <c r="D173" s="13"/>
-      <c r="E173" s="13"/>
-      <c r="F173" s="13"/>
-      <c r="G173" s="13"/>
-      <c r="H173" s="13"/>
-      <c r="I173" s="13"/>
-      <c r="J173" s="13"/>
+      <c r="D173" s="12"/>
+      <c r="E173" s="12"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
+      <c r="H173" s="12"/>
+      <c r="I173" s="12"/>
+      <c r="J173" s="12"/>
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
       <c r="M173" s="12"/>
@@ -23106,13 +23505,13 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="5"/>
-      <c r="D174" s="13"/>
-      <c r="E174" s="13"/>
-      <c r="F174" s="13"/>
-      <c r="G174" s="13"/>
-      <c r="H174" s="13"/>
-      <c r="I174" s="13"/>
-      <c r="J174" s="13"/>
+      <c r="D174" s="12"/>
+      <c r="E174" s="12"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12"/>
+      <c r="H174" s="12"/>
+      <c r="I174" s="12"/>
+      <c r="J174" s="12"/>
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
       <c r="M174" s="12"/>
@@ -23128,13 +23527,13 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="5"/>
-      <c r="D175" s="13"/>
-      <c r="E175" s="13"/>
-      <c r="F175" s="13"/>
-      <c r="G175" s="13"/>
-      <c r="H175" s="13"/>
-      <c r="I175" s="13"/>
-      <c r="J175" s="13"/>
+      <c r="D175" s="12"/>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12"/>
+      <c r="H175" s="12"/>
+      <c r="I175" s="12"/>
+      <c r="J175" s="12"/>
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
       <c r="M175" s="12"/>
@@ -23150,13 +23549,13 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="5"/>
-      <c r="D176" s="13"/>
-      <c r="E176" s="13"/>
-      <c r="F176" s="13"/>
-      <c r="G176" s="13"/>
-      <c r="H176" s="13"/>
-      <c r="I176" s="13"/>
-      <c r="J176" s="13"/>
+      <c r="D176" s="12"/>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12"/>
+      <c r="H176" s="12"/>
+      <c r="I176" s="12"/>
+      <c r="J176" s="12"/>
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
       <c r="M176" s="12"/>
@@ -23172,13 +23571,13 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="5"/>
-      <c r="D177" s="13"/>
-      <c r="E177" s="13"/>
-      <c r="F177" s="13"/>
-      <c r="G177" s="13"/>
-      <c r="H177" s="13"/>
-      <c r="I177" s="13"/>
-      <c r="J177" s="13"/>
+      <c r="D177" s="12"/>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12"/>
+      <c r="H177" s="12"/>
+      <c r="I177" s="12"/>
+      <c r="J177" s="12"/>
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
       <c r="M177" s="12"/>
@@ -23194,13 +23593,13 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="5"/>
-      <c r="D178" s="13"/>
-      <c r="E178" s="13"/>
-      <c r="F178" s="13"/>
-      <c r="G178" s="13"/>
-      <c r="H178" s="13"/>
-      <c r="I178" s="13"/>
-      <c r="J178" s="13"/>
+      <c r="D178" s="12"/>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12"/>
+      <c r="H178" s="12"/>
+      <c r="I178" s="12"/>
+      <c r="J178" s="12"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
       <c r="M178" s="12"/>
@@ -23216,13 +23615,13 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="5"/>
-      <c r="D179" s="13"/>
-      <c r="E179" s="13"/>
-      <c r="F179" s="13"/>
-      <c r="G179" s="13"/>
-      <c r="H179" s="13"/>
-      <c r="I179" s="13"/>
-      <c r="J179" s="13"/>
+      <c r="D179" s="12"/>
+      <c r="E179" s="12"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12"/>
+      <c r="H179" s="12"/>
+      <c r="I179" s="12"/>
+      <c r="J179" s="12"/>
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
       <c r="M179" s="12"/>
@@ -23238,13 +23637,13 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="5"/>
-      <c r="D180" s="13"/>
-      <c r="E180" s="13"/>
-      <c r="F180" s="13"/>
-      <c r="G180" s="13"/>
-      <c r="H180" s="13"/>
-      <c r="I180" s="13"/>
-      <c r="J180" s="13"/>
+      <c r="D180" s="12"/>
+      <c r="E180" s="12"/>
+      <c r="F180" s="12"/>
+      <c r="G180" s="12"/>
+      <c r="H180" s="12"/>
+      <c r="I180" s="12"/>
+      <c r="J180" s="12"/>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
       <c r="M180" s="12"/>
@@ -23260,13 +23659,13 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="5"/>
-      <c r="D181" s="13"/>
-      <c r="E181" s="13"/>
-      <c r="F181" s="13"/>
-      <c r="G181" s="13"/>
-      <c r="H181" s="13"/>
-      <c r="I181" s="13"/>
-      <c r="J181" s="13"/>
+      <c r="D181" s="12"/>
+      <c r="E181" s="12"/>
+      <c r="F181" s="12"/>
+      <c r="G181" s="12"/>
+      <c r="H181" s="12"/>
+      <c r="I181" s="12"/>
+      <c r="J181" s="12"/>
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
       <c r="M181" s="12"/>
@@ -23282,13 +23681,13 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="5"/>
-      <c r="D182" s="13"/>
-      <c r="E182" s="13"/>
-      <c r="F182" s="13"/>
-      <c r="G182" s="13"/>
-      <c r="H182" s="13"/>
-      <c r="I182" s="13"/>
-      <c r="J182" s="13"/>
+      <c r="D182" s="12"/>
+      <c r="E182" s="12"/>
+      <c r="F182" s="12"/>
+      <c r="G182" s="12"/>
+      <c r="H182" s="12"/>
+      <c r="I182" s="12"/>
+      <c r="J182" s="12"/>
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
       <c r="M182" s="12"/>
@@ -23304,13 +23703,13 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="5"/>
-      <c r="D183" s="13"/>
-      <c r="E183" s="13"/>
-      <c r="F183" s="13"/>
-      <c r="G183" s="13"/>
-      <c r="H183" s="13"/>
-      <c r="I183" s="13"/>
-      <c r="J183" s="13"/>
+      <c r="D183" s="12"/>
+      <c r="E183" s="12"/>
+      <c r="F183" s="12"/>
+      <c r="G183" s="12"/>
+      <c r="H183" s="12"/>
+      <c r="I183" s="12"/>
+      <c r="J183" s="12"/>
       <c r="K183" s="2"/>
       <c r="L183" s="2"/>
       <c r="M183" s="12"/>
@@ -23326,13 +23725,13 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="5"/>
-      <c r="D184" s="13"/>
-      <c r="E184" s="13"/>
-      <c r="F184" s="13"/>
-      <c r="G184" s="13"/>
-      <c r="H184" s="13"/>
-      <c r="I184" s="13"/>
-      <c r="J184" s="13"/>
+      <c r="D184" s="12"/>
+      <c r="E184" s="12"/>
+      <c r="F184" s="12"/>
+      <c r="G184" s="12"/>
+      <c r="H184" s="12"/>
+      <c r="I184" s="12"/>
+      <c r="J184" s="12"/>
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
       <c r="M184" s="12"/>
@@ -23348,13 +23747,13 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="5"/>
-      <c r="D185" s="13"/>
-      <c r="E185" s="13"/>
-      <c r="F185" s="13"/>
-      <c r="G185" s="13"/>
-      <c r="H185" s="13"/>
-      <c r="I185" s="13"/>
-      <c r="J185" s="13"/>
+      <c r="D185" s="12"/>
+      <c r="E185" s="12"/>
+      <c r="F185" s="12"/>
+      <c r="G185" s="12"/>
+      <c r="H185" s="12"/>
+      <c r="I185" s="12"/>
+      <c r="J185" s="12"/>
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
       <c r="M185" s="12"/>
@@ -23370,13 +23769,13 @@
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="5"/>
-      <c r="D186" s="13"/>
-      <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
-      <c r="G186" s="13"/>
-      <c r="H186" s="13"/>
-      <c r="I186" s="13"/>
-      <c r="J186" s="13"/>
+      <c r="D186" s="12"/>
+      <c r="E186" s="12"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
+      <c r="H186" s="12"/>
+      <c r="I186" s="12"/>
+      <c r="J186" s="12"/>
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
       <c r="M186" s="12"/>
@@ -23392,13 +23791,13 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="5"/>
-      <c r="D187" s="13"/>
-      <c r="E187" s="13"/>
-      <c r="F187" s="13"/>
-      <c r="G187" s="13"/>
-      <c r="H187" s="13"/>
-      <c r="I187" s="13"/>
-      <c r="J187" s="13"/>
+      <c r="D187" s="12"/>
+      <c r="E187" s="12"/>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12"/>
+      <c r="H187" s="12"/>
+      <c r="I187" s="12"/>
+      <c r="J187" s="12"/>
       <c r="K187" s="2"/>
       <c r="L187" s="2"/>
       <c r="M187" s="12"/>
@@ -23414,13 +23813,13 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="5"/>
-      <c r="D188" s="13"/>
-      <c r="E188" s="13"/>
-      <c r="F188" s="13"/>
-      <c r="G188" s="13"/>
-      <c r="H188" s="13"/>
-      <c r="I188" s="13"/>
-      <c r="J188" s="13"/>
+      <c r="D188" s="12"/>
+      <c r="E188" s="12"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
+      <c r="H188" s="12"/>
+      <c r="I188" s="12"/>
+      <c r="J188" s="12"/>
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
       <c r="M188" s="12"/>
@@ -23436,13 +23835,13 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="5"/>
-      <c r="D189" s="13"/>
-      <c r="E189" s="13"/>
-      <c r="F189" s="13"/>
-      <c r="G189" s="13"/>
-      <c r="H189" s="13"/>
-      <c r="I189" s="13"/>
-      <c r="J189" s="13"/>
+      <c r="D189" s="12"/>
+      <c r="E189" s="12"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
+      <c r="H189" s="12"/>
+      <c r="I189" s="12"/>
+      <c r="J189" s="12"/>
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
       <c r="M189" s="12"/>
@@ -23458,13 +23857,13 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="5"/>
-      <c r="D190" s="13"/>
-      <c r="E190" s="13"/>
-      <c r="F190" s="13"/>
-      <c r="G190" s="13"/>
-      <c r="H190" s="13"/>
-      <c r="I190" s="13"/>
-      <c r="J190" s="13"/>
+      <c r="D190" s="12"/>
+      <c r="E190" s="12"/>
+      <c r="F190" s="12"/>
+      <c r="G190" s="12"/>
+      <c r="H190" s="12"/>
+      <c r="I190" s="12"/>
+      <c r="J190" s="12"/>
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
       <c r="M190" s="12"/>
@@ -23480,13 +23879,13 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="5"/>
-      <c r="D191" s="13"/>
-      <c r="E191" s="13"/>
-      <c r="F191" s="13"/>
-      <c r="G191" s="13"/>
-      <c r="H191" s="13"/>
-      <c r="I191" s="13"/>
-      <c r="J191" s="13"/>
+      <c r="D191" s="12"/>
+      <c r="E191" s="12"/>
+      <c r="F191" s="12"/>
+      <c r="G191" s="12"/>
+      <c r="H191" s="12"/>
+      <c r="I191" s="12"/>
+      <c r="J191" s="12"/>
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
       <c r="M191" s="12"/>
@@ -23502,13 +23901,13 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="5"/>
-      <c r="D192" s="13"/>
-      <c r="E192" s="13"/>
-      <c r="F192" s="13"/>
-      <c r="G192" s="13"/>
-      <c r="H192" s="13"/>
-      <c r="I192" s="13"/>
-      <c r="J192" s="13"/>
+      <c r="D192" s="12"/>
+      <c r="E192" s="12"/>
+      <c r="F192" s="12"/>
+      <c r="G192" s="12"/>
+      <c r="H192" s="12"/>
+      <c r="I192" s="12"/>
+      <c r="J192" s="12"/>
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
       <c r="M192" s="12"/>
@@ -23524,13 +23923,13 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="5"/>
-      <c r="D193" s="13"/>
-      <c r="E193" s="13"/>
-      <c r="F193" s="13"/>
-      <c r="G193" s="13"/>
-      <c r="H193" s="13"/>
-      <c r="I193" s="13"/>
-      <c r="J193" s="13"/>
+      <c r="D193" s="12"/>
+      <c r="E193" s="12"/>
+      <c r="F193" s="12"/>
+      <c r="G193" s="12"/>
+      <c r="H193" s="12"/>
+      <c r="I193" s="12"/>
+      <c r="J193" s="12"/>
       <c r="K193" s="2"/>
       <c r="L193" s="2"/>
       <c r="M193" s="12"/>
@@ -23546,13 +23945,13 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="5"/>
-      <c r="D194" s="13"/>
-      <c r="E194" s="13"/>
-      <c r="F194" s="13"/>
-      <c r="G194" s="13"/>
-      <c r="H194" s="13"/>
-      <c r="I194" s="13"/>
-      <c r="J194" s="13"/>
+      <c r="D194" s="12"/>
+      <c r="E194" s="12"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
+      <c r="H194" s="12"/>
+      <c r="I194" s="12"/>
+      <c r="J194" s="12"/>
       <c r="K194" s="2"/>
       <c r="L194" s="2"/>
       <c r="M194" s="12"/>
@@ -23568,13 +23967,13 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="5"/>
-      <c r="D195" s="13"/>
-      <c r="E195" s="13"/>
-      <c r="F195" s="13"/>
-      <c r="G195" s="13"/>
-      <c r="H195" s="13"/>
-      <c r="I195" s="13"/>
-      <c r="J195" s="13"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="12"/>
+      <c r="F195" s="12"/>
+      <c r="G195" s="12"/>
+      <c r="H195" s="12"/>
+      <c r="I195" s="12"/>
+      <c r="J195" s="12"/>
       <c r="K195" s="2"/>
       <c r="L195" s="2"/>
       <c r="M195" s="12"/>
@@ -23590,13 +23989,13 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="5"/>
-      <c r="D196" s="13"/>
-      <c r="E196" s="13"/>
-      <c r="F196" s="13"/>
-      <c r="G196" s="13"/>
-      <c r="H196" s="13"/>
-      <c r="I196" s="13"/>
-      <c r="J196" s="13"/>
+      <c r="D196" s="12"/>
+      <c r="E196" s="12"/>
+      <c r="F196" s="12"/>
+      <c r="G196" s="12"/>
+      <c r="H196" s="12"/>
+      <c r="I196" s="12"/>
+      <c r="J196" s="12"/>
       <c r="K196" s="2"/>
       <c r="L196" s="2"/>
       <c r="M196" s="12"/>
@@ -23612,13 +24011,13 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="5"/>
-      <c r="D197" s="13"/>
-      <c r="E197" s="13"/>
-      <c r="F197" s="13"/>
-      <c r="G197" s="13"/>
-      <c r="H197" s="13"/>
-      <c r="I197" s="13"/>
-      <c r="J197" s="13"/>
+      <c r="D197" s="12"/>
+      <c r="E197" s="12"/>
+      <c r="F197" s="12"/>
+      <c r="G197" s="12"/>
+      <c r="H197" s="12"/>
+      <c r="I197" s="12"/>
+      <c r="J197" s="12"/>
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
       <c r="M197" s="12"/>
@@ -23634,13 +24033,13 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="5"/>
-      <c r="D198" s="13"/>
-      <c r="E198" s="13"/>
-      <c r="F198" s="13"/>
-      <c r="G198" s="13"/>
-      <c r="H198" s="13"/>
-      <c r="I198" s="13"/>
-      <c r="J198" s="13"/>
+      <c r="D198" s="12"/>
+      <c r="E198" s="12"/>
+      <c r="F198" s="12"/>
+      <c r="G198" s="12"/>
+      <c r="H198" s="12"/>
+      <c r="I198" s="12"/>
+      <c r="J198" s="12"/>
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
       <c r="M198" s="12"/>
@@ -23656,13 +24055,13 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="5"/>
-      <c r="D199" s="13"/>
-      <c r="E199" s="13"/>
-      <c r="F199" s="13"/>
-      <c r="G199" s="13"/>
-      <c r="H199" s="13"/>
-      <c r="I199" s="13"/>
-      <c r="J199" s="13"/>
+      <c r="D199" s="12"/>
+      <c r="E199" s="12"/>
+      <c r="F199" s="12"/>
+      <c r="G199" s="12"/>
+      <c r="H199" s="12"/>
+      <c r="I199" s="12"/>
+      <c r="J199" s="12"/>
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
       <c r="M199" s="12"/>
@@ -23678,13 +24077,13 @@
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="5"/>
-      <c r="D200" s="13"/>
-      <c r="E200" s="13"/>
-      <c r="F200" s="13"/>
-      <c r="G200" s="13"/>
-      <c r="H200" s="13"/>
-      <c r="I200" s="13"/>
-      <c r="J200" s="13"/>
+      <c r="D200" s="12"/>
+      <c r="E200" s="12"/>
+      <c r="F200" s="12"/>
+      <c r="G200" s="12"/>
+      <c r="H200" s="12"/>
+      <c r="I200" s="12"/>
+      <c r="J200" s="12"/>
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
       <c r="M200" s="12"/>
@@ -23700,13 +24099,13 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="5"/>
-      <c r="D201" s="13"/>
-      <c r="E201" s="13"/>
-      <c r="F201" s="13"/>
-      <c r="G201" s="13"/>
-      <c r="H201" s="13"/>
-      <c r="I201" s="13"/>
-      <c r="J201" s="13"/>
+      <c r="D201" s="12"/>
+      <c r="E201" s="12"/>
+      <c r="F201" s="12"/>
+      <c r="G201" s="12"/>
+      <c r="H201" s="12"/>
+      <c r="I201" s="12"/>
+      <c r="J201" s="12"/>
       <c r="K201" s="2"/>
       <c r="L201" s="2"/>
       <c r="M201" s="12"/>

--- a/data/Edison's Scores.xlsx
+++ b/data/Edison's Scores.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="USKids"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="640">
   <si>
     <t>Course</t>
   </si>
@@ -1915,6 +1915,27 @@
   </si>
   <si>
     <t>5,365,4,3,7,Y</t>
+  </si>
+  <si>
+    <t>5,404,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,312,3,4,7,Y</t>
+  </si>
+  <si>
+    <t>3,108,1,2,3,Y</t>
+  </si>
+  <si>
+    <t>4,281,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>3,107,2,1,3,X</t>
+  </si>
+  <si>
+    <t>4,277,4,1,5,X</t>
+  </si>
+  <si>
+    <t>4,288,2,1,3,Y</t>
   </si>
 </sst>
 </file>
@@ -5258,7 +5279,7 @@
       <c r="A72" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C72" s="3">
@@ -5299,7 +5320,7 @@
       <c r="A73" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C73" s="3">
@@ -5340,7 +5361,7 @@
       <c r="A74" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C74" s="3">
@@ -5381,7 +5402,7 @@
       <c r="A75" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C75" s="3">
@@ -5422,7 +5443,7 @@
       <c r="A76" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C76" s="3">
@@ -5463,7 +5484,7 @@
       <c r="A77" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C77" s="3">
@@ -5501,19 +5522,45 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
-      <c r="A78" s="2"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="12"/>
+      <c r="A78" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" s="3">
+        <v>46173</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="M78" s="12">
+        <v>39</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
       <c r="A79" s="2"/>
@@ -19843,7 +19890,7 @@
       <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C13" s="3">
@@ -19885,7 +19932,7 @@
       <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="3">
@@ -19927,7 +19974,7 @@
       <c r="A15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="3">
@@ -19969,7 +20016,7 @@
       <c r="A16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="3">
@@ -20011,7 +20058,7 @@
       <c r="A17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C17" s="3">
@@ -20053,7 +20100,7 @@
       <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="3">
@@ -20092,16 +20139,36 @@
       <c r="T18" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46173</v>
+      </c>
+      <c r="D19" s="12">
+        <v>56</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>2</v>
+      </c>
+      <c r="I19" s="12">
+        <v>2</v>
+      </c>
+      <c r="J19" s="12">
+        <v>39</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="12"/>

--- a/data/Edison's Scores.xlsx
+++ b/data/Edison's Scores.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="USKids"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="655">
   <si>
     <t>Course</t>
   </si>
@@ -1936,6 +1936,51 @@
   </si>
   <si>
     <t>4,288,2,1,3,Y</t>
+  </si>
+  <si>
+    <t>5,427,4,2,6,Y</t>
+  </si>
+  <si>
+    <t>4,293,2,3,5,X</t>
+  </si>
+  <si>
+    <t>4,320,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>3,130,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,335,2,2,4,X</t>
+  </si>
+  <si>
+    <t>5,405,6,3,9,Y</t>
+  </si>
+  <si>
+    <t>4,295,3,1,4,X</t>
+  </si>
+  <si>
+    <t>3,125,1,3,4,Y</t>
+  </si>
+  <si>
+    <t>5,405,5,2,7,X</t>
+  </si>
+  <si>
+    <t>4,290,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>4,275,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,300,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>3,120,2,2,4,X</t>
+  </si>
+  <si>
+    <t>5,400,3,3,6,Y</t>
+  </si>
+  <si>
+    <t>4,279,3,2,5,Y</t>
   </si>
 </sst>
 </file>
@@ -5563,34 +5608,86 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
-      <c r="A79" s="2"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="12"/>
+      <c r="A79" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C79" s="3">
+        <v>46180</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="M79" s="12">
+        <v>46</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
-      <c r="A80" s="2"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="12"/>
+      <c r="A80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C80" s="3">
+        <v>46187</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="M80" s="12">
+        <v>44</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
       <c r="A81" s="2"/>
@@ -20181,16 +20278,36 @@
       <c r="T19" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46180</v>
+      </c>
+      <c r="D20" s="12">
+        <v>45</v>
+      </c>
+      <c r="E20" s="12">
+        <v>6</v>
+      </c>
+      <c r="F20" s="12">
+        <v>1</v>
+      </c>
+      <c r="G20" s="12">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12">
+        <v>2</v>
+      </c>
+      <c r="I20" s="12">
+        <v>3</v>
+      </c>
+      <c r="J20" s="12">
+        <v>46</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="12"/>
@@ -20203,16 +20320,36 @@
       <c r="T20" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
+      <c r="A21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="5">
+        <v>46187</v>
+      </c>
+      <c r="D21" s="12">
+        <v>39</v>
+      </c>
+      <c r="E21" s="12">
+        <v>5</v>
+      </c>
+      <c r="F21" s="12">
+        <v>2</v>
+      </c>
+      <c r="G21" s="12">
+        <v>2</v>
+      </c>
+      <c r="H21" s="12">
+        <v>2</v>
+      </c>
+      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="J21" s="12">
+        <v>44</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="12"/>

--- a/data/Edison's Scores.xlsx
+++ b/data/Edison's Scores.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="699">
   <si>
     <t>Course</t>
   </si>
@@ -180,6 +180,12 @@
     <t>PGA National - Back</t>
   </si>
   <si>
+    <t>Legacy - Front</t>
+  </si>
+  <si>
+    <t>Legacy - Back</t>
+  </si>
+  <si>
     <t>Turtle Creek</t>
   </si>
   <si>
@@ -1981,6 +1987,132 @@
   </si>
   <si>
     <t>4,279,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,251,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>5,440,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,289,2,4,6,X</t>
+  </si>
+  <si>
+    <t>4,278,2,3,5,Y</t>
+  </si>
+  <si>
+    <t>5,419,3,2,5,X</t>
+  </si>
+  <si>
+    <t>4,302,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>4,238,2,3,5,Y</t>
+  </si>
+  <si>
+    <t>3,121,2,3,5,Y</t>
+  </si>
+  <si>
+    <t>4,255,2,2,4,X</t>
+  </si>
+  <si>
+    <t>3,107,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,306,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>5,415,4,1,5,X</t>
+  </si>
+  <si>
+    <t>4,233,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,312,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>3,102,1,1,2,Y</t>
+  </si>
+  <si>
+    <t>5,408,3,3,6,Y</t>
+  </si>
+  <si>
+    <t>4,251,2,2,4,X</t>
+  </si>
+  <si>
+    <t>5,440,4,1,5,Y</t>
+  </si>
+  <si>
+    <t>4,289,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,278,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,302,2,3,5,Y</t>
+  </si>
+  <si>
+    <t>4,238,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>3,121,4,2,6,X</t>
+  </si>
+  <si>
+    <t>3,107,1,1,2,Y</t>
+  </si>
+  <si>
+    <t>4,306,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,233,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>4,312,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>4,280,3,1,4,Y</t>
+  </si>
+  <si>
+    <t>3,102,1,2,3,Y</t>
+  </si>
+  <si>
+    <t>4,251,3,1,4,X</t>
+  </si>
+  <si>
+    <t>5,440,3,3,6,X</t>
+  </si>
+  <si>
+    <t>4,289,4,2,6,X</t>
+  </si>
+  <si>
+    <t>4,278,3,2,5,X</t>
+  </si>
+  <si>
+    <t>5,419,3,3,6,X</t>
+  </si>
+  <si>
+    <t>4,302,2,1,3,Y</t>
+  </si>
+  <si>
+    <t>3,121,1,2,3,Y</t>
+  </si>
+  <si>
+    <t>4,255,2,2,4,Y</t>
+  </si>
+  <si>
+    <t>3,107,4,1,5,X</t>
+  </si>
+  <si>
+    <t>5,415,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,233,2,1,3,Y</t>
+  </si>
+  <si>
+    <t>4,312,2,2,4,X</t>
+  </si>
+  <si>
+    <t>5,408,3,2,5,Y</t>
   </si>
 </sst>
 </file>
@@ -2452,40 +2584,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3">
         <v>44661</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M2" s="15">
         <v>57</v>
@@ -2496,37 +2628,37 @@
         <v>45</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3">
         <v>44677</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M3" s="15">
         <v>51</v>
@@ -2537,37 +2669,37 @@
         <v>46</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3">
         <v>44682</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M4" s="15">
         <v>50</v>
@@ -2578,37 +2710,37 @@
         <v>49</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
         <v>44696</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M5" s="15">
         <v>52</v>
@@ -2619,37 +2751,37 @@
         <v>46</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3">
         <v>44709</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M6" s="15">
         <v>53</v>
@@ -2660,37 +2792,37 @@
         <v>43</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3">
         <v>44737</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M7" s="15">
         <v>52</v>
@@ -2701,37 +2833,37 @@
         <v>45</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3">
         <v>44849</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M8" s="15">
         <v>45</v>
@@ -2742,37 +2874,37 @@
         <v>46</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="3">
         <v>44863</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M9" s="15">
         <v>54</v>
@@ -2783,37 +2915,37 @@
         <v>43</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3">
         <v>44870</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M10" s="15">
         <v>46</v>
@@ -2824,37 +2956,37 @@
         <v>46</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3">
         <v>44878</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M11" s="15">
         <v>52</v>
@@ -2862,40 +2994,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3">
         <v>44884</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="M12" s="15">
         <v>45</v>
@@ -2906,37 +3038,37 @@
         <v>43</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3">
         <v>44898</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M13" s="15">
         <v>45</v>
@@ -2947,37 +3079,37 @@
         <v>46</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C14" s="3">
         <v>45017</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M14" s="15">
         <v>52</v>
@@ -2985,40 +3117,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
       <c r="A15" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C15" s="3">
         <v>45031</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M15" s="15">
         <v>49</v>
@@ -3029,37 +3161,37 @@
         <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="3">
         <v>45052</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M16" s="15">
         <v>38</v>
@@ -3070,37 +3202,37 @@
         <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C17" s="3">
         <v>45053</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M17" s="15">
         <v>54</v>
@@ -3111,37 +3243,37 @@
         <v>43</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C18" s="3">
         <v>45073</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M18" s="15">
         <v>46</v>
@@ -3149,40 +3281,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3">
         <v>45081</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="M19" s="15">
         <v>46</v>
@@ -3193,37 +3325,37 @@
         <v>45</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3">
         <v>45087</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M20" s="15">
         <v>41</v>
@@ -3231,40 +3363,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3">
         <v>45088</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M21" s="15">
         <v>47</v>
@@ -3272,40 +3404,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="20.25">
       <c r="A22" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C22" s="3">
         <v>45116</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I22" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="L22" s="17" t="s">
         <v>206</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>204</v>
       </c>
       <c r="M22" s="12">
         <v>45</v>
@@ -3313,40 +3445,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C23" s="3">
         <v>45129</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M23" s="12">
         <v>45</v>
@@ -3354,40 +3486,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="20.25">
       <c r="A24" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C24" s="3">
         <v>45165</v>
       </c>
       <c r="D24" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="H24" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="17" t="s">
         <v>218</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>216</v>
       </c>
       <c r="M24" s="12">
         <v>45</v>
@@ -3395,40 +3527,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
       <c r="A25" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C25" s="3">
         <v>45171</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L25" s="17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M25" s="12">
         <v>47</v>
@@ -3436,40 +3568,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
       <c r="A26" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C26" s="3">
         <v>45172</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M26" s="12">
         <v>45</v>
@@ -3477,40 +3609,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.25">
       <c r="A27" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C27" s="3">
         <v>45179</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M27" s="12">
         <v>49</v>
@@ -3518,40 +3650,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.25">
       <c r="A28" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C28" s="3">
         <v>45186</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M28" s="12">
         <v>41</v>
@@ -3559,40 +3691,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.25">
       <c r="A29" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C29" s="3">
         <v>45206</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M29" s="12">
         <v>42</v>
@@ -3600,40 +3732,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.25">
       <c r="A30" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C30" s="3">
         <v>45207</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M30" s="12">
         <v>42</v>
@@ -3641,40 +3773,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20.25">
       <c r="A31" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C31" s="3">
         <v>45208</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M31" s="12">
         <v>49</v>
@@ -3682,40 +3814,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="20.25">
       <c r="A32" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C32" s="3">
         <v>45220</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M32" s="12">
         <v>39</v>
@@ -3726,37 +3858,37 @@
         <v>49</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C33" s="3">
         <v>45221</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M33" s="12">
         <v>42</v>
@@ -3764,40 +3896,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20.25">
       <c r="A34" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C34" s="5">
         <v>45228</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M34" s="12">
         <v>45</v>
@@ -3808,37 +3940,37 @@
         <v>43</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C35" s="3">
         <v>45253</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M35" s="12">
         <v>43</v>
@@ -3846,40 +3978,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.25">
       <c r="A36" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C36" s="5">
         <v>45249</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M36" s="12">
         <v>41</v>
@@ -3890,37 +4022,37 @@
         <v>46</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C37" s="3">
         <v>45298</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M37" s="12">
         <v>42</v>
@@ -3928,40 +4060,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="20.25">
       <c r="A38" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C38" s="3">
         <v>45306</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M38" s="12">
         <v>39</v>
@@ -3969,40 +4101,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="20.25">
       <c r="A39" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C39" s="3">
         <v>45307</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M39" s="12">
         <v>40</v>
@@ -4010,40 +4142,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="20.25">
       <c r="A40" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C40" s="3">
         <v>45389</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M40" s="12">
         <v>46</v>
@@ -4054,37 +4186,37 @@
         <v>45</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C41" s="3">
         <v>45396</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M41" s="12">
         <v>44</v>
@@ -4095,37 +4227,37 @@
         <v>49</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C42" s="3">
         <v>45409</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M42" s="12">
         <v>44</v>
@@ -4136,37 +4268,37 @@
         <v>46</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C43" s="3">
         <v>45410</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M43" s="12">
         <v>50</v>
@@ -4174,40 +4306,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.25">
       <c r="A44" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C44" s="3">
         <v>45445</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="I44" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J44" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="K44" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="L44" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M44" s="12">
         <v>44</v>
@@ -4215,40 +4347,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="20.25">
       <c r="A45" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C45" s="3">
         <v>45451</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M45" s="12">
         <v>44</v>
@@ -4256,40 +4388,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="20.25">
       <c r="A46" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C46" s="3">
         <v>45452</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M46" s="12">
         <v>48</v>
@@ -4297,40 +4429,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="20.25">
       <c r="A47" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C47" s="3">
         <v>45466</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M47" s="12">
         <v>50</v>
@@ -4338,40 +4470,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="20.25">
       <c r="A48" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C48" s="3">
         <v>45472</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M48" s="12">
         <v>38</v>
@@ -4379,40 +4511,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="20.25">
       <c r="A49" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C49" s="3">
         <v>45478</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M49" s="12">
         <v>40</v>
@@ -4420,40 +4552,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="20.25">
       <c r="A50" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C50" s="3">
         <v>45479</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M50" s="12">
         <v>43</v>
@@ -4461,40 +4593,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="20.25">
       <c r="A51" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C51" s="3">
         <v>45494</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M51" s="12">
         <v>43</v>
@@ -4505,37 +4637,37 @@
         <v>45</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C52" s="3">
         <v>45584</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M52" s="12">
         <v>44</v>
@@ -4546,37 +4678,37 @@
         <v>46</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C53" s="3">
         <v>45599</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M53" s="12">
         <v>45</v>
@@ -4584,40 +4716,40 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C54" s="3">
         <v>45606</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M54" s="12">
         <v>42</v>
@@ -4628,37 +4760,37 @@
         <v>43</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C55" s="3">
         <v>45619</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M55" s="12">
         <v>46</v>
@@ -4669,37 +4801,37 @@
         <v>49</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C56" s="3">
         <v>45620</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M56" s="12">
         <v>45</v>
@@ -4716,31 +4848,31 @@
         <v>45753</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M57" s="12">
         <v>44</v>
@@ -4757,31 +4889,31 @@
         <v>45781</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M58" s="12">
         <v>41</v>
@@ -4798,31 +4930,31 @@
         <v>45795</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M59" s="12">
         <v>44</v>
@@ -4839,31 +4971,31 @@
         <v>45815</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M60" s="12">
         <v>44</v>
@@ -4880,31 +5012,31 @@
         <v>45816</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M61" s="12">
         <v>47</v>
@@ -4921,31 +5053,31 @@
         <v>45934</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M62" s="12">
         <v>43</v>
@@ -4962,31 +5094,31 @@
         <v>45935</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M63" s="12">
         <v>38</v>
@@ -4994,7 +5126,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>44</v>
@@ -5003,31 +5135,31 @@
         <v>45941</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M64" s="12">
         <v>42</v>
@@ -5035,7 +5167,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>44</v>
@@ -5044,31 +5176,31 @@
         <v>45941</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M65" s="12">
         <v>41</v>
@@ -5076,7 +5208,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>44</v>
@@ -5085,31 +5217,31 @@
         <v>45942</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M66" s="12">
         <v>44</v>
@@ -5117,7 +5249,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>44</v>
@@ -5126,31 +5258,31 @@
         <v>45942</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M67" s="12">
         <v>46</v>
@@ -5167,31 +5299,31 @@
         <v>45956</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M68" s="12">
         <v>41</v>
@@ -5208,31 +5340,31 @@
         <v>45984</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M69" s="12">
         <v>44</v>
@@ -5249,31 +5381,31 @@
         <v>45991</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M70" s="12">
         <v>36</v>
@@ -5290,31 +5422,31 @@
         <v>45998</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M71" s="12">
         <v>40</v>
@@ -5331,31 +5463,31 @@
         <v>46131</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M72" s="12">
         <v>46</v>
@@ -5372,31 +5504,31 @@
         <v>46133</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M73" s="12">
         <v>42</v>
@@ -5413,37 +5545,37 @@
         <v>46158</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M74" s="12">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="2" t="s">
         <v>53</v>
       </c>
@@ -5454,37 +5586,37 @@
         <v>46158</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M75" s="12">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="2" t="s">
         <v>52</v>
       </c>
@@ -5495,37 +5627,37 @@
         <v>46159</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M76" s="12">
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="2" t="s">
         <v>53</v>
       </c>
@@ -5536,37 +5668,37 @@
         <v>46159</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M77" s="12">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="2" t="s">
         <v>50</v>
       </c>
@@ -5577,209 +5709,365 @@
         <v>46173</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="M78" s="12">
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C79" s="3">
         <v>46180</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M79" s="12">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C80" s="3">
         <v>46187</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M80" s="12">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
-      <c r="A81" s="2"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
-      <c r="A82" s="2"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
-      <c r="A83" s="2"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
-      <c r="A84" s="2"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
-      <c r="A85" s="2"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
-      <c r="A86" s="2"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="12"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
+      <c r="A81" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" s="3">
+        <v>46233</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="M81" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
+      <c r="A82" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="3">
+        <v>46233</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="M82" s="12">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
+      <c r="A83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C83" s="3">
+        <v>46234</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="M83" s="12">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
+      <c r="A84" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84" s="3">
+        <v>46234</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="M84" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
+      <c r="A85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C85" s="3">
+        <v>46235</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="M85" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
+      <c r="A86" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C86" s="3">
+        <v>46235</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="M86" s="12">
+        <v>37</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="2"/>
       <c r="B87" s="12"/>
       <c r="C87" s="3"/>
@@ -5794,7 +6082,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="2"/>
       <c r="B88" s="12"/>
       <c r="C88" s="3"/>
@@ -5809,7 +6097,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="2"/>
       <c r="B89" s="12"/>
       <c r="C89" s="3"/>
@@ -5824,7 +6112,7 @@
       <c r="L89" s="2"/>
       <c r="M89" s="12"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="2"/>
       <c r="B90" s="12"/>
       <c r="C90" s="3"/>
@@ -20362,16 +20650,36 @@
       <c r="T21" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
+      <c r="A22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="3">
+        <v>46233</v>
+      </c>
+      <c r="D22" s="12">
+        <v>32</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12">
+        <v>5</v>
+      </c>
+      <c r="I22" s="12">
+        <v>2</v>
+      </c>
+      <c r="J22" s="12">
+        <v>42</v>
+      </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="12"/>
@@ -20384,16 +20692,36 @@
       <c r="T22" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="A23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46233</v>
+      </c>
+      <c r="D23" s="12">
+        <v>46</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>1</v>
+      </c>
+      <c r="H23" s="12">
+        <v>1</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12">
+        <v>38</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="12"/>
@@ -20406,16 +20734,36 @@
       <c r="T23" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
+      <c r="A24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46234</v>
+      </c>
+      <c r="D24" s="12">
+        <v>26</v>
+      </c>
+      <c r="E24" s="12">
+        <v>3</v>
+      </c>
+      <c r="F24" s="12">
+        <v>3</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12">
+        <v>1</v>
+      </c>
+      <c r="I24" s="12">
+        <v>2</v>
+      </c>
+      <c r="J24" s="12">
+        <v>40</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="12"/>
@@ -20428,16 +20776,36 @@
       <c r="T24" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
+      <c r="A25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46234</v>
+      </c>
+      <c r="D25" s="12">
+        <v>47</v>
+      </c>
+      <c r="E25" s="12">
+        <v>0</v>
+      </c>
+      <c r="F25" s="12">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12">
+        <v>1</v>
+      </c>
+      <c r="I25" s="12">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12">
+        <v>36</v>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="12"/>
@@ -20450,16 +20818,36 @@
       <c r="T25" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
+      <c r="A26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46235</v>
+      </c>
+      <c r="D26" s="12">
+        <v>17</v>
+      </c>
+      <c r="E26" s="12">
+        <v>1</v>
+      </c>
+      <c r="F26" s="12">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12">
+        <v>2</v>
+      </c>
+      <c r="H26" s="12">
+        <v>2</v>
+      </c>
+      <c r="I26" s="12">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12">
+        <v>40</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="12"/>
@@ -20472,16 +20860,36 @@
       <c r="T26" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
+      <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46235</v>
+      </c>
+      <c r="D27" s="12">
+        <v>18</v>
+      </c>
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+      <c r="F27" s="12">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12">
+        <v>0</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0</v>
+      </c>
+      <c r="I27" s="12">
+        <v>1</v>
+      </c>
+      <c r="J27" s="12">
+        <v>37</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="12"/>
